--- a/prep_and_checklists/Bumble  /PREPLIST_Bumble  _02-04-2026_0.xlsx
+++ b/prep_and_checklists/Bumble  /PREPLIST_Bumble  _02-04-2026_0.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Bumble  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B4AD8C-6C63-0845-8F44-8E8F44606A06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9599DD42-FD3F-EA44-95EC-312A140E126E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_sheet" sheetId="1" r:id="rId1"/>
     <sheet name="order_sheet" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
   <si>
     <t xml:space="preserve">Bumble  , Guests: 30   , 6:00 PM - 9:00 PM   ,Tuesday, February 10, 2026  </t>
   </si>
@@ -324,13 +337,16 @@
   </si>
   <si>
     <t>30 pcs, see Req Prep</t>
+  </si>
+  <si>
+    <t>630 STARTER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,34 +362,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -384,6 +372,40 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="3">
@@ -440,27 +462,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -765,303 +789,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="4" max="4" width="52.1640625" customWidth="1"/>
     <col min="5" max="5" width="33.83203125" customWidth="1"/>
     <col min="7" max="7" width="29.83203125" customWidth="1"/>
     <col min="10" max="10" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="5" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="7"/>
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="D4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D23" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="1:5" ht="19" x14ac:dyDescent="0.2">
-      <c r="D24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D25" s="3" t="s">
+    </row>
+    <row r="25" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="D26" s="3" t="s">
+    <row r="26" spans="1:5" s="8" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="11" t="s">
         <v>100</v>
       </c>
     </row>
+    <row r="27" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:B4"/>
@@ -1072,7 +1100,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup scale="51" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -1082,14 +1110,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -1103,267 +1131,268 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="19" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>